--- a/output/pdf_financials_xlsx/NSE.xlsx
+++ b/output/pdf_financials_xlsx/NSE.xlsx
@@ -1071,10 +1071,10 @@
         <v>-2.879299</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.848084</v>
+        <v>-1.848084</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.406555</v>
+        <v>-1.406555</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-1.090988</v>
@@ -1279,10 +1279,10 @@
         <v>-2.879299</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.848084</v>
+        <v>-1.848084</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.406555</v>
+        <v>-1.406555</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-1.090988</v>
@@ -1405,10 +1405,10 @@
         <v>-2.879299</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.848084</v>
+        <v>-1.848084</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.406555</v>
+        <v>-1.406555</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-1.090988</v>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>36.96168</v>
+        <v>-36.96168</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>35.163875</v>
+        <v>-35.163875</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>-54.5494</v>
@@ -1615,10 +1615,10 @@
         <v>-2.879299</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.848084</v>
+        <v>-1.848084</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.406555</v>
+        <v>-1.406555</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.090988</v>
@@ -1699,10 +1699,10 @@
         <v>-2.879299</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.848084</v>
+        <v>-1.848084</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.406555</v>
+        <v>-1.406555</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.090988</v>
@@ -1801,10 +1801,10 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -39113,13 +39113,13 @@
         </is>
       </c>
       <c r="I466" s="5" t="n">
-        <v>1.848084</v>
+        <v>-1.848084</v>
       </c>
       <c r="J466" s="5" t="n">
-        <v>1.406555</v>
+        <v>-1.406555</v>
       </c>
       <c r="K466" s="5" t="n">
-        <v>1.090988</v>
+        <v>-1.090988</v>
       </c>
       <c r="L466" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NSE.xlsx
+++ b/output/pdf_financials_xlsx/NSE.xlsx
@@ -802,22 +802,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.315003</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.156934</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>2.879299</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.848084</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1.406555</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>1.090988</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>10.712403</v>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.315003</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-1.406555</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -1905,13 +1905,13 @@
         <v>0.004707</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.561929</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.029429</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.252865</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.8673920000000001</v>
@@ -1985,13 +1985,13 @@
         <v>0.004707</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.561929</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.029429</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.252865</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.8673920000000001</v>
@@ -2465,13 +2465,13 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.659923</v>
+        <v>0.097994</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.031729</v>
+        <v>0.0023</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.258092</v>
+        <v>0.005227</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -38738,7 +38738,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -39018,7 +39018,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -40087,7 +40087,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -40785,7 +40785,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">

--- a/output/pdf_financials_xlsx/NSE.xlsx
+++ b/output/pdf_financials_xlsx/NSE.xlsx
@@ -528,10 +528,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -578,10 +576,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -620,10 +616,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -670,10 +664,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -712,10 +704,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -754,10 +744,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -796,10 +784,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.321823</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.315003</v>
@@ -838,10 +824,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.321823</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.315003</v>
@@ -888,10 +872,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -930,10 +912,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -972,10 +952,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -1014,10 +992,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>1.3e-05</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -1056,10 +1032,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.32181</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.315003</v>
@@ -1098,10 +1072,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1122,7 +1094,7 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.98356</v>
+        <v>-2.6e-05</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>0.003883</v>
@@ -1264,10 +1236,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.32181</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.315003</v>
@@ -1294,10 +1264,10 @@
         <v>-11.350072</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-32.477345</v>
+        <v>-11.516361</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-27.714253</v>
+        <v>-15.025015</v>
       </c>
     </row>
     <row r="21">
@@ -1306,10 +1276,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1336,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-20.960984</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-12.689238</v>
       </c>
     </row>
     <row r="22">
@@ -1348,10 +1316,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1390,10 +1356,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.32181</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.315003</v>
@@ -1600,10 +1564,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.32181</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.315003</v>
@@ -1642,10 +1604,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1684,10 +1644,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.32181</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.315003</v>
@@ -1786,10 +1744,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1810,7 +1766,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>16.74058053381487</v>
+        <v>0.0001458844782337833</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0.03419953663723346</v>
@@ -3238,13 +3194,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -4508,10 +4464,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.32181</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.315003</v>
@@ -4550,10 +4504,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4592,10 +4544,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -4634,10 +4584,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -4676,10 +4624,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -4718,10 +4664,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.14582</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.18476</v>
@@ -4760,10 +4704,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -4802,10 +4744,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.14582</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.18476</v>
@@ -4844,10 +4784,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -4886,10 +4824,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -4928,10 +4864,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -4970,10 +4904,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5012,10 +4944,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -5054,10 +4984,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5096,10 +5024,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5138,10 +5064,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -5180,10 +5104,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5222,10 +5144,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -5264,10 +5184,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -5306,10 +5224,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -5348,10 +5264,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.010085</v>
@@ -5400,10 +5314,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -5442,10 +5354,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -5469,10 +5379,10 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.099111</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
@@ -5484,10 +5394,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -5526,10 +5434,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -5568,10 +5474,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -5610,10 +5514,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -5652,10 +5554,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -5756,10 +5656,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -5798,10 +5696,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.081569</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.050517</v>
@@ -5846,10 +5742,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.003512</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.004555</v>
@@ -5888,10 +5782,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -5930,10 +5822,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.001043</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.001821</v>
@@ -5972,10 +5862,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.004555</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.002734</v>
@@ -6014,10 +5902,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6056,10 +5942,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.080526</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.042253</v>
@@ -6113,7 +5997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O494"/>
+  <dimension ref="A1:O501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19906,7 +19790,11 @@
           <t>Share repurchases 20</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -22000,7 +21888,11 @@
           <t>Share repurchases 17</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -23994,7 +23886,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -30016,10 +29912,8 @@
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E338" s="5" t="n">
+        <v>0.001654</v>
       </c>
       <c r="F338" s="5" t="n">
         <v>0.00171</v>
@@ -30085,10 +29979,8 @@
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E339" s="5" t="n">
+        <v>0.09365999999999999</v>
       </c>
       <c r="F339" s="5" t="n">
         <v>0.093917</v>
@@ -30154,10 +30046,8 @@
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E340" s="5" t="n">
+        <v>0.00015</v>
       </c>
       <c r="F340" s="5" t="n">
         <v>-0.007637</v>
@@ -30227,10 +30117,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E341" s="5" t="n">
+        <v>0.14582</v>
       </c>
       <c r="F341" s="5" t="n">
         <v>0.18476</v>
@@ -30300,10 +30188,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E342" s="5" t="n">
+        <v>-0.080526</v>
       </c>
       <c r="F342" s="5" t="n">
         <v>-0.042253</v>
@@ -30369,10 +30255,8 @@
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E343" s="5" t="n">
+        <v>0.081569</v>
       </c>
       <c r="F343" s="5" t="n">
         <v>0.050517</v>
@@ -30442,10 +30326,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E344" s="5" t="n">
+        <v>0.081569</v>
       </c>
       <c r="F344" s="5" t="n">
         <v>0.050517</v>
@@ -30661,10 +30543,8 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E347" s="5" t="n">
+        <v>0.001043</v>
       </c>
       <c r="F347" s="5" t="n">
         <v>-0.001821</v>
@@ -30876,10 +30756,8 @@
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E350" s="5" t="n">
+        <v>-0.754641</v>
       </c>
       <c r="F350" s="5" t="n">
         <v>-0.754641</v>
@@ -30950,10 +30828,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F351" s="5" t="n">
+        <v>0.157062</v>
       </c>
       <c r="G351" s="5" t="n">
         <v>0.157062</v>
@@ -31020,10 +30896,8 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E352" s="5" t="n">
+        <v>-0.32181</v>
       </c>
       <c r="F352" s="5" t="n">
         <v>-0.315003</v>
@@ -31089,10 +30963,8 @@
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E353" s="5" t="n">
+        <v>-1.069644</v>
       </c>
       <c r="F353" s="5" t="n">
         <v>-1.069644</v>
@@ -31284,33 +31156,29 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>(Restated Note 32)</t>
+          <t>Purchases of mineral properties, machinery,</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>General and administrative 21</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="n">
+        <v>0.003512</v>
+      </c>
+      <c r="F356" s="5" t="n">
+        <v>0.004555</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
@@ -31347,39 +31215,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N356" s="5" t="n">
-        <v>-14.29014</v>
-      </c>
-      <c r="O356" s="5" t="n">
-        <v>-8.862147999999999</v>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>(Restated Note 32)</t>
+          <t>Purchases of mineral properties, machinery,</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Stock-based compensation 20</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="n">
+        <v>0.004555</v>
+      </c>
+      <c r="F357" s="5" t="n">
+        <v>0.002734</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -31416,8 +31288,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N357" s="5" t="n">
-        <v>-0.494185</v>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -31428,20 +31302,24 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>(226,616)          1,143,597   Foreign exchange (loss) / gain</t>
+          <t>Supplementary information</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Guarantee provision expense 19</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -31492,24 +31370,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O358" s="5" t="n">
-        <v>-1.289639</v>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>771,096          7,697,351   Other income                                                 22</t>
+          <t>Supplementary information</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Operating loss from continuing operations</t>
+          <t>Taxes paid</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -31558,39 +31438,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N359" s="5" t="n">
-        <v>-7.268527</v>
-      </c>
-      <c r="O359" s="5" t="n">
-        <v>-9.607307</v>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>771,096          7,697,351   Other income                                                 22</t>
+          <t>Shares issued       Share capital            costs            shares           surplus                              Deficiency</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Finance cost, net 23</t>
+          <t>As at March 31, 2014 51,137,679 $12,252,841 ($1,106,476) $256,617 $214,467</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E360" s="5" t="n">
+        <v>-0.432831</v>
+      </c>
+      <c r="F360" s="5" t="n">
+        <v>-11.793663</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -31627,27 +31507,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N360" s="5" t="n">
-        <v>-2.675275</v>
-      </c>
-      <c r="O360" s="5" t="n">
-        <v>-3.123229</v>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>771,096          7,697,351   Other income                                                 22</t>
+          <t>Shares issued       Share capital            costs            shares           surplus                              Deficiency</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Net loss before income taxes from continuing operations</t>
+          <t>Expired stock options - - - - ($47,692)</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -31656,10 +31540,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F361" s="5" t="n">
+        <v>0.047692</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -31696,11 +31578,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N361" s="5" t="n">
-        <v>-9.943802</v>
-      </c>
-      <c r="O361" s="5" t="n">
-        <v>-12.730536</v>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -31711,15 +31597,19 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>(Restated Note 32)</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Current 24</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr"/>
+          <t>General and administrative 21</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -31766,10 +31656,10 @@
         </is>
       </c>
       <c r="N362" s="5" t="n">
-        <v>-1.572559</v>
+        <v>-14.29014</v>
       </c>
       <c r="O362" s="5" t="n">
-        <v>-0.01449</v>
+        <v>-8.862147999999999</v>
       </c>
     </row>
     <row r="363">
@@ -31780,12 +31670,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>(Restated Note 32)</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Deferred 24</t>
+          <t>Stock-based compensation 20</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -31834,13 +31724,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O363" s="5" t="n">
-        <v>-2.279989</v>
+      <c r="N363" s="5" t="n">
+        <v>-0.494185</v>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -31851,12 +31741,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>(226,616)          1,143,597   Foreign exchange (loss) / gain</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations</t>
+          <t>Guarantee provision expense 19</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -31905,11 +31795,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N364" s="5" t="n">
-        <v>-11.516361</v>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O364" s="5" t="n">
-        <v>-15.025015</v>
+        <v>-1.289639</v>
       </c>
     </row>
     <row r="365">
@@ -31920,12 +31812,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Discontinued operations</t>
+          <t>771,096          7,697,351   Other income                                                 22</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Loss on disposal of discontinued operations 13(a,b)</t>
+          <t>Operating loss from continuing operations</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -31975,10 +31867,10 @@
         </is>
       </c>
       <c r="N365" s="5" t="n">
-        <v>-14.707266</v>
+        <v>-7.268527</v>
       </c>
       <c r="O365" s="5" t="n">
-        <v>-11.020531</v>
+        <v>-9.607307</v>
       </c>
     </row>
     <row r="366">
@@ -31989,19 +31881,15 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Discontinued operations</t>
+          <t>771,096          7,697,351   Other income                                                 22</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Finance cost, net 23</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -32048,10 +31936,10 @@
         </is>
       </c>
       <c r="N366" s="5" t="n">
-        <v>-2.017976</v>
+        <v>-2.675275</v>
       </c>
       <c r="O366" s="5" t="n">
-        <v>1.460956</v>
+        <v>-3.123229</v>
       </c>
     </row>
     <row r="367">
@@ -32062,12 +31950,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Accretion loss on the loan commitment of discontinued</t>
+          <t>771,096          7,697,351   Other income                                                 22</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Accretion loss on the loan commitment of discontinued operations 14(b)</t>
+          <t>Net loss before income taxes from continuing operations</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -32117,10 +32005,10 @@
         </is>
       </c>
       <c r="N367" s="5" t="n">
-        <v>-4.235742</v>
+        <v>-9.943802</v>
       </c>
       <c r="O367" s="5" t="n">
-        <v>-3.129663</v>
+        <v>-12.730536</v>
       </c>
     </row>
     <row r="368">
@@ -32131,12 +32019,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Accretion loss on the loan commitment of discontinued</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Net loss from discontinued operations</t>
+          <t>Current 24</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -32186,10 +32074,10 @@
         </is>
       </c>
       <c r="N368" s="5" t="n">
-        <v>-20.960984</v>
+        <v>-1.572559</v>
       </c>
       <c r="O368" s="5" t="n">
-        <v>-12.689238</v>
+        <v>-0.01449</v>
       </c>
     </row>
     <row r="369">
@@ -32200,19 +32088,15 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Accretion loss on the loan commitment of discontinued</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred 24</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -32258,11 +32142,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N369" s="5" t="n">
-        <v>-32.477345</v>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O369" s="5" t="n">
-        <v>-27.714253</v>
+        <v>-2.279989</v>
       </c>
     </row>
     <row r="370">
@@ -32273,15 +32159,19 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Exchange  differences  in  translation  of  the  companies'</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Exchange  differences  in  translation  of  the  companies' subsidiaries.</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>Net loss from continuing operations</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -32322,14 +32212,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M370" s="5" t="n">
-        <v>-1.493341</v>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N370" s="5" t="n">
-        <v>0.047172</v>
+        <v>-11.516361</v>
       </c>
       <c r="O370" s="5" t="n">
-        <v>-0.350413</v>
+        <v>-15.025015</v>
       </c>
     </row>
     <row r="371">
@@ -32340,19 +32232,15 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Exchange  differences  in  translation  of  the  companies'</t>
+          <t>Discontinued operations</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on disposal of discontinued operations 13(a,b)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -32393,14 +32281,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M371" s="5" t="n">
-        <v>-12.843413</v>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N371" s="5" t="n">
-        <v>-32.430173</v>
+        <v>-14.707266</v>
       </c>
       <c r="O371" s="5" t="n">
-        <v>-28.064666</v>
+        <v>-11.020531</v>
       </c>
     </row>
     <row r="372">
@@ -32411,17 +32301,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Basic and diluted from discontinued operations                                                                 $(0.10)               $(0.16)</t>
+          <t>Discontinued operations</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Foreign exchange gain</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -32470,10 +32360,10 @@
         </is>
       </c>
       <c r="N372" s="5" t="n">
-        <v>128.765626</v>
+        <v>-2.017976</v>
       </c>
       <c r="O372" s="5" t="n">
-        <v>133.945901</v>
+        <v>1.460956</v>
       </c>
     </row>
     <row r="373">
@@ -32484,12 +32374,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Accretion loss on the loan commitment of discontinued</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year 20 $</t>
+          <t>Accretion loss on the loan commitment of discontinued operations 14(b)</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -32539,10 +32429,10 @@
         </is>
       </c>
       <c r="N373" s="5" t="n">
-        <v>31.828122</v>
+        <v>-4.235742</v>
       </c>
       <c r="O373" s="5" t="n">
-        <v>36.932501</v>
+        <v>-3.129663</v>
       </c>
     </row>
     <row r="374">
@@ -32553,15 +32443,19 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Accretion loss on the loan commitment of discontinued</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Share repurchase 20</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr"/>
+          <t>Net loss from discontinued operations</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -32608,12 +32502,10 @@
         </is>
       </c>
       <c r="N374" s="5" t="n">
-        <v>-0.099111</v>
-      </c>
-      <c r="O374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-20.960984</v>
+      </c>
+      <c r="O374" s="5" t="n">
+        <v>-12.689238</v>
       </c>
     </row>
     <row r="375">
@@ -32624,15 +32516,19 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Accretion loss on the loan commitment of discontinued</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Warrants exercise 20</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -32679,12 +32575,10 @@
         </is>
       </c>
       <c r="N375" s="5" t="n">
-        <v>5.17249</v>
-      </c>
-      <c r="O375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-32.477345</v>
+      </c>
+      <c r="O375" s="5" t="n">
+        <v>-27.714253</v>
       </c>
     </row>
     <row r="376">
@@ -32695,12 +32589,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Exchange  differences  in  translation  of  the  companies'</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Options exercise 20</t>
+          <t>Exchange  differences  in  translation  of  the  companies' subsidiaries.</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -32744,16 +32638,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M376" s="5" t="n">
+        <v>-1.493341</v>
       </c>
       <c r="N376" s="5" t="n">
-        <v>0.031</v>
+        <v>0.047172</v>
       </c>
       <c r="O376" s="5" t="n">
-        <v>0.027632</v>
+        <v>-0.350413</v>
       </c>
     </row>
     <row r="377">
@@ -32764,15 +32656,19 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Exchange  differences  in  translation  of  the  companies'</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Balance, end of the year</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -32813,16 +32709,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M377" s="5" t="n">
+        <v>-12.843413</v>
       </c>
       <c r="N377" s="5" t="n">
-        <v>36.932501</v>
+        <v>-32.430173</v>
       </c>
       <c r="O377" s="5" t="n">
-        <v>36.960133</v>
+        <v>-28.064666</v>
       </c>
     </row>
     <row r="378">
@@ -32833,15 +32727,19 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Warrants</t>
+          <t>Basic and diluted from discontinued operations                                                                 $(0.10)               $(0.16)</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -32882,16 +32780,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M378" s="5" t="n">
-        <v>1.26001</v>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N378" s="5" t="n">
-        <v>1.142388</v>
-      </c>
-      <c r="O378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>128.765626</v>
+      </c>
+      <c r="O378" s="5" t="n">
+        <v>133.945901</v>
       </c>
     </row>
     <row r="379">
@@ -32902,12 +32800,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Warrants</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Fair value of warrants exercised 20</t>
+          <t>Balance, beginning of the year 20 $</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -32957,12 +32855,10 @@
         </is>
       </c>
       <c r="N379" s="5" t="n">
-        <v>-0.90182</v>
-      </c>
-      <c r="O379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>31.828122</v>
+      </c>
+      <c r="O379" s="5" t="n">
+        <v>36.932501</v>
       </c>
     </row>
     <row r="380">
@@ -32973,12 +32869,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Warrants</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Warrants expired 20</t>
+          <t>Share repurchase 20</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -33028,7 +32924,7 @@
         </is>
       </c>
       <c r="N380" s="5" t="n">
-        <v>-0.240568</v>
+        <v>-0.099111</v>
       </c>
       <c r="O380" t="inlineStr">
         <is>
@@ -33044,12 +32940,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Warrants</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Balance, end of the year</t>
+          <t>Warrants exercise 20</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -33093,13 +32989,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M381" s="5" t="n">
-        <v>1.142388</v>
-      </c>
-      <c r="N381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N381" s="5" t="n">
+        <v>5.17249</v>
       </c>
       <c r="O381" t="inlineStr">
         <is>
@@ -33115,12 +33011,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year</t>
+          <t>Options exercise 20</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -33164,14 +33060,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M382" s="5" t="n">
-        <v>4.316215</v>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N382" s="5" t="n">
-        <v>4.316215</v>
+        <v>0.031</v>
       </c>
       <c r="O382" s="5" t="n">
-        <v>5.050968</v>
+        <v>0.027632</v>
       </c>
     </row>
     <row r="383">
@@ -33182,12 +33080,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Warrants expired</t>
+          <t>Balance, end of the year</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -33237,12 +33135,10 @@
         </is>
       </c>
       <c r="N383" s="5" t="n">
-        <v>0.240568</v>
-      </c>
-      <c r="O383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>36.932501</v>
+      </c>
+      <c r="O383" s="5" t="n">
+        <v>36.960133</v>
       </c>
     </row>
     <row r="384">
@@ -33253,12 +33149,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Warrants</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Balance, beginning of the year</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -33302,13 +33198,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M384" s="5" t="n">
+        <v>1.26001</v>
       </c>
       <c r="N384" s="5" t="n">
-        <v>0.494185</v>
+        <v>1.142388</v>
       </c>
       <c r="O384" t="inlineStr">
         <is>
@@ -33324,12 +33218,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Warrants</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Options exercise</t>
+          <t>Fair value of warrants exercised 20</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -33378,13 +33272,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O385" s="5" t="n">
-        <v>-0.022832</v>
+      <c r="N385" s="5" t="n">
+        <v>-0.90182</v>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="386">
@@ -33395,12 +33289,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
+          <t>Warrants</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Balance, end of the year</t>
+          <t>Warrants expired 20</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -33444,14 +33338,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M386" s="5" t="n">
-        <v>4.316215</v>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N386" s="5" t="n">
-        <v>5.050968</v>
-      </c>
-      <c r="O386" s="5" t="n">
-        <v>5.028136</v>
+        <v>-0.240568</v>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="387">
@@ -33462,12 +33360,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment</t>
+          <t>Warrants</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year</t>
+          <t>Balance, end of the year</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -33512,13 +33410,17 @@
         </is>
       </c>
       <c r="M387" s="5" t="n">
-        <v>1.315932</v>
-      </c>
-      <c r="N387" s="5" t="n">
-        <v>-0.177408</v>
-      </c>
-      <c r="O387" s="5" t="n">
-        <v>-0.130236</v>
+        <v>1.142388</v>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="388">
@@ -33529,12 +33431,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Translation reserve</t>
+          <t>Balance, beginning of the year</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -33579,13 +33481,13 @@
         </is>
       </c>
       <c r="M388" s="5" t="n">
-        <v>-1.49334</v>
+        <v>4.316215</v>
       </c>
       <c r="N388" s="5" t="n">
-        <v>0.047172</v>
+        <v>4.316215</v>
       </c>
       <c r="O388" s="5" t="n">
-        <v>-0.350413</v>
+        <v>5.050968</v>
       </c>
     </row>
     <row r="389">
@@ -33596,12 +33498,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Balance, end of the year</t>
+          <t>Warrants expired</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -33645,14 +33547,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M389" s="5" t="n">
-        <v>-0.177408</v>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N389" s="5" t="n">
-        <v>-0.130236</v>
-      </c>
-      <c r="O389" s="5" t="n">
-        <v>-0.480649</v>
+        <v>0.240568</v>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="390">
@@ -33663,12 +33569,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -33712,14 +33618,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M390" s="5" t="n">
-        <v>-3.699474</v>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N390" s="5" t="n">
-        <v>-15.049546</v>
-      </c>
-      <c r="O390" s="5" t="n">
-        <v>-47.526891</v>
+        <v>0.494185</v>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="391">
@@ -33730,19 +33640,15 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Options exercise</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -33783,14 +33689,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M391" s="5" t="n">
-        <v>-11.350072</v>
-      </c>
-      <c r="N391" s="5" t="n">
-        <v>-32.477345</v>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O391" s="5" t="n">
-        <v>-27.714253</v>
+        <v>-0.022832</v>
       </c>
     </row>
     <row r="392">
@@ -33801,7 +33711,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -33851,13 +33761,13 @@
         </is>
       </c>
       <c r="M392" s="5" t="n">
-        <v>-15.049546</v>
+        <v>4.316215</v>
       </c>
       <c r="N392" s="5" t="n">
-        <v>-47.526891</v>
+        <v>5.050968</v>
       </c>
       <c r="O392" s="5" t="n">
-        <v>-75.24114400000001</v>
+        <v>5.028136</v>
       </c>
     </row>
     <row r="393">
@@ -33868,12 +33778,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Cumulative translation adjustment</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Total shareholders' (deficit) equity $</t>
+          <t>Balance, beginning of the year</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -33918,13 +33828,13 @@
         </is>
       </c>
       <c r="M393" s="5" t="n">
-        <v>22.059771</v>
+        <v>1.315932</v>
       </c>
       <c r="N393" s="5" t="n">
-        <v>-5.673658</v>
+        <v>-0.177408</v>
       </c>
       <c r="O393" s="5" t="n">
-        <v>-33.733524</v>
+        <v>-0.130236</v>
       </c>
     </row>
     <row r="394">
@@ -33933,17 +33843,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment</t>
+        </is>
+      </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>General and administrative 18</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Translation reserve</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -33985,15 +33895,13 @@
         </is>
       </c>
       <c r="M394" s="5" t="n">
-        <v>-17.108396</v>
+        <v>-1.49334</v>
       </c>
       <c r="N394" s="5" t="n">
-        <v>-14.5076</v>
-      </c>
-      <c r="O394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.047172</v>
+      </c>
+      <c r="O394" s="5" t="n">
+        <v>-0.350413</v>
       </c>
     </row>
     <row r="395">
@@ -34002,10 +33910,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustment</t>
+        </is>
+      </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Income from investments in Joint Venture 10</t>
+          <t>Balance, end of the year</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -34049,18 +33961,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M395" s="5" t="n">
+        <v>-0.177408</v>
       </c>
       <c r="N395" s="5" t="n">
-        <v>1.663979</v>
-      </c>
-      <c r="O395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.130236</v>
+      </c>
+      <c r="O395" s="5" t="n">
+        <v>-0.480649</v>
       </c>
     </row>
     <row r="396">
@@ -34069,10 +33977,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Accumulated deficit</t>
+        </is>
+      </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Stock-based compensation 17</t>
+          <t>Balance, beginning of the year</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -34116,18 +34028,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M396" s="5" t="n">
+        <v>-3.699474</v>
       </c>
       <c r="N396" s="5" t="n">
-        <v>-0.494185</v>
-      </c>
-      <c r="O396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-15.049546</v>
+      </c>
+      <c r="O396" s="5" t="n">
+        <v>-47.526891</v>
       </c>
     </row>
     <row r="397">
@@ -34138,15 +34046,19 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>7,697,351          7,006,965   Other income                                                  20</t>
+          <t>Accumulated deficit</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Operating loss from continuing operations</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -34188,15 +34100,13 @@
         </is>
       </c>
       <c r="M397" s="5" t="n">
-        <v>-10.619062</v>
+        <v>-11.350072</v>
       </c>
       <c r="N397" s="5" t="n">
-        <v>-7.839984</v>
-      </c>
-      <c r="O397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-32.477345</v>
+      </c>
+      <c r="O397" s="5" t="n">
+        <v>-27.714253</v>
       </c>
     </row>
     <row r="398">
@@ -34207,12 +34117,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>7,697,351          7,006,965   Other income                                                  20</t>
+          <t>Accumulated deficit</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Financial cost ,net 19</t>
+          <t>Balance, end of the year</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -34257,15 +34167,13 @@
         </is>
       </c>
       <c r="M398" s="5" t="n">
-        <v>-0.727127</v>
+        <v>-15.049546</v>
       </c>
       <c r="N398" s="5" t="n">
-        <v>-2.675275</v>
-      </c>
-      <c r="O398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-47.526891</v>
+      </c>
+      <c r="O398" s="5" t="n">
+        <v>-75.24114400000001</v>
       </c>
     </row>
     <row r="399">
@@ -34276,12 +34184,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>7,697,351          7,006,965   Other income                                                  20</t>
+          <t>Accumulated deficit</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Net loss before income taxes from continuing operations</t>
+          <t>Total shareholders' (deficit) equity $</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -34326,15 +34234,13 @@
         </is>
       </c>
       <c r="M399" s="5" t="n">
-        <v>-11.346189</v>
+        <v>22.059771</v>
       </c>
       <c r="N399" s="5" t="n">
-        <v>-14.751001</v>
-      </c>
-      <c r="O399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.673658</v>
+      </c>
+      <c r="O399" s="5" t="n">
+        <v>-33.733524</v>
       </c>
     </row>
     <row r="400">
@@ -34343,19 +34249,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>7,697,351          7,006,965   Other income                                                  20</t>
-        </is>
-      </c>
+      <c r="B400" t="inlineStr"/>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Income tax expense 21</t>
+          <t>General and administrative 18</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -34399,10 +34301,10 @@
         </is>
       </c>
       <c r="M400" s="5" t="n">
-        <v>-0.003883</v>
+        <v>-17.108396</v>
       </c>
       <c r="N400" s="5" t="n">
-        <v>-1.572559</v>
+        <v>-14.5076</v>
       </c>
       <c r="O400" t="inlineStr">
         <is>
@@ -34416,14 +34318,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>7,697,351          7,006,965   Other income                                                  20</t>
-        </is>
-      </c>
+      <c r="B401" t="inlineStr"/>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations</t>
+          <t>Income from investments in Joint Venture 10</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -34467,11 +34365,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M401" s="5" t="n">
-        <v>-11.350072</v>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N401" s="5" t="n">
-        <v>-16.32356</v>
+        <v>1.663979</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
@@ -34485,14 +34385,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Discontinued operations</t>
-        </is>
-      </c>
+      <c r="B402" t="inlineStr"/>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Income from discontinued operations 11</t>
+          <t>Stock-based compensation 17</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -34542,7 +34438,7 @@
         </is>
       </c>
       <c r="N402" s="5" t="n">
-        <v>4.639305</v>
+        <v>-0.494185</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
@@ -34558,19 +34454,15 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Discontinued operations</t>
+          <t>7,697,351          7,006,965   Other income                                                  20</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Loss on disposal of discontinued operations 11</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>GainsLossOnDisposalOfDiscontinuedOperations</t>
-        </is>
-      </c>
+          <t>Operating loss from continuing operations</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -34611,13 +34503,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M403" s="5" t="n">
+        <v>-10.619062</v>
       </c>
       <c r="N403" s="5" t="n">
-        <v>-19.980723</v>
+        <v>-7.839984</v>
       </c>
       <c r="O403" t="inlineStr">
         <is>
@@ -34633,12 +34523,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Discontinued operations</t>
+          <t>7,697,351          7,006,965   Other income                                                  20</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Net loss from discontinued operations</t>
+          <t>Financial cost ,net 19</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -34682,13 +34572,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M404" s="5" t="n">
+        <v>-0.727127</v>
       </c>
       <c r="N404" s="5" t="n">
-        <v>-15.341418</v>
+        <v>-2.675275</v>
       </c>
       <c r="O404" t="inlineStr">
         <is>
@@ -34704,19 +34592,15 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Discontinued operations</t>
+          <t>7,697,351          7,006,965   Other income                                                  20</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Net loss before income taxes from continuing operations</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -34758,10 +34642,10 @@
         </is>
       </c>
       <c r="M405" s="5" t="n">
-        <v>-11.350072</v>
+        <v>-11.346189</v>
       </c>
       <c r="N405" s="5" t="n">
-        <v>-31.664978</v>
+        <v>-14.751001</v>
       </c>
       <c r="O405" t="inlineStr">
         <is>
@@ -34777,15 +34661,19 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>7,697,351          7,006,965   Other income                                                  20</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Balance, beginning of the year 17 $</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr"/>
+          <t>Income tax expense 21</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -34827,10 +34715,10 @@
         </is>
       </c>
       <c r="M406" s="5" t="n">
-        <v>31.227085</v>
+        <v>-0.003883</v>
       </c>
       <c r="N406" s="5" t="n">
-        <v>31.828122</v>
+        <v>-1.572559</v>
       </c>
       <c r="O406" t="inlineStr">
         <is>
@@ -34846,15 +34734,19 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>7,697,351          7,006,965   Other income                                                  20</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Share repurchase 17</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr"/>
+          <t>Net loss from continuing operations</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -34895,13 +34787,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M407" s="5" t="n">
+        <v>-11.350072</v>
       </c>
       <c r="N407" s="5" t="n">
-        <v>-0.099111</v>
+        <v>-16.32356</v>
       </c>
       <c r="O407" t="inlineStr">
         <is>
@@ -34917,15 +34807,19 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Discontinued operations</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Warrants exercise 17</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>Income from discontinued operations 11</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -34966,11 +34860,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M408" s="5" t="n">
-        <v>0.5938369999999999</v>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N408" s="5" t="n">
-        <v>5.17249</v>
+        <v>4.639305</v>
       </c>
       <c r="O408" t="inlineStr">
         <is>
@@ -34986,15 +34882,19 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Discontinued operations</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Options exercise 17</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>Loss on disposal of discontinued operations 11</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>GainsLossOnDisposalOfDiscontinuedOperations</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -35035,11 +34935,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M409" s="5" t="n">
-        <v>0.0072</v>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N409" s="5" t="n">
-        <v>0.031</v>
+        <v>-19.980723</v>
       </c>
       <c r="O409" t="inlineStr">
         <is>
@@ -35055,15 +34957,19 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Discontinued operations</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Balance, end of the year 36,</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>Net loss from discontinued operations</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -35104,11 +35010,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M410" s="5" t="n">
-        <v>31.828122</v>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N410" s="5" t="n">
-        <v>0.932501</v>
+        <v>-15.341418</v>
       </c>
       <c r="O410" t="inlineStr">
         <is>
@@ -35124,15 +35032,19 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Warrants</t>
+          <t>Discontinued operations</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Fair value of warrants exercised 17</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -35174,10 +35086,10 @@
         </is>
       </c>
       <c r="M411" s="5" t="n">
-        <v>-0.117622</v>
+        <v>-11.350072</v>
       </c>
       <c r="N411" s="5" t="n">
-        <v>-0.90182</v>
+        <v>-31.664978</v>
       </c>
       <c r="O411" t="inlineStr">
         <is>
@@ -35193,12 +35105,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Warrants</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Warrants expired 17</t>
+          <t>Balance, beginning of the year 17 $</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -35242,13 +35154,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M412" s="5" t="n">
+        <v>31.227085</v>
       </c>
       <c r="N412" s="5" t="n">
-        <v>-0.240568</v>
+        <v>31.828122</v>
       </c>
       <c r="O412" t="inlineStr">
         <is>
@@ -35264,12 +35174,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>For the nine         For the</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>December 31, March</t>
+          <t>Share repurchase 17</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -35308,18 +35218,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L413" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N413" s="5" t="n">
+        <v>-0.099111</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
@@ -35335,12 +35245,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Services Revenue 17 $ 83,370,906 $</t>
+          <t>Warrants exercise 17</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -35379,18 +35289,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L414" s="5" t="n">
-        <v>24.83227</v>
-      </c>
-      <c r="M414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M414" s="5" t="n">
+        <v>0.5938369999999999</v>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>5.17249</v>
       </c>
       <c r="O414" t="inlineStr">
         <is>
@@ -35406,12 +35314,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Operator fees 688,272</t>
+          <t>Options exercise 17</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -35450,18 +35358,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L415" s="5" t="n">
-        <v>0.150089</v>
-      </c>
-      <c r="M415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M415" s="5" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="N415" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="O415" t="inlineStr">
         <is>
@@ -35477,12 +35383,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Technical Services 9,245,666</t>
+          <t>Balance, end of the year 36,</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -35521,18 +35427,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L416" s="5" t="n">
-        <v>0.729748</v>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M416" s="5" t="n">
+        <v>31.828122</v>
+      </c>
+      <c r="N416" s="5" t="n">
+        <v>0.932501</v>
       </c>
       <c r="O416" t="inlineStr">
         <is>
@@ -35548,12 +35452,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Warrants</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Income total</t>
+          <t>Fair value of warrants exercised 17</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -35592,18 +35496,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L417" s="5" t="n">
-        <v>25.712107</v>
-      </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M417" s="5" t="n">
+        <v>-0.117622</v>
+      </c>
+      <c r="N417" s="5" t="n">
+        <v>-0.90182</v>
       </c>
       <c r="O417" t="inlineStr">
         <is>
@@ -35619,19 +35521,15 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Warrants</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Operating expenses 18 53,382,575</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Warrants expired 17</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -35667,18 +35565,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L418" s="5" t="n">
-        <v>10.712403</v>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N418" s="5" t="n">
+        <v>-0.240568</v>
       </c>
       <c r="O418" t="inlineStr">
         <is>
@@ -35694,19 +35592,15 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>For the nine         For the</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Depletion and depreciation 9 21,807,111</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>December 31, March</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -35743,7 +35637,7 @@
         </is>
       </c>
       <c r="L419" s="5" t="n">
-        <v>7.75032</v>
+        <v>3.1e-05</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
@@ -35769,19 +35663,15 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Gross profit 18,115,158</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Services Revenue 17 $ 83,370,906 $</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -35818,7 +35708,7 @@
         </is>
       </c>
       <c r="L420" s="5" t="n">
-        <v>7.249384</v>
+        <v>24.83227</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -35844,19 +35734,15 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>General and administrative 19 8,997,959</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Operator fees 688,272</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -35893,7 +35779,7 @@
         </is>
       </c>
       <c r="L421" s="5" t="n">
-        <v>4.215798</v>
+        <v>0.150089</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -35919,12 +35805,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Financial cost (income) 21 95,995</t>
+          <t>Technical Services 9,245,666</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -35964,7 +35850,7 @@
         </is>
       </c>
       <c r="L422" s="5" t="n">
-        <v>-0.167621</v>
+        <v>0.729748</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
@@ -35990,12 +35876,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Stock-based compensation 12 2,802,659</t>
+          <t>Income total</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -36035,7 +35921,7 @@
         </is>
       </c>
       <c r="L423" s="5" t="n">
-        <v>0.767899</v>
+        <v>25.712107</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -36066,10 +35952,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (365,910)</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>Operating expenses 18 53,382,575</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -36106,7 +35996,7 @@
         </is>
       </c>
       <c r="L424" s="5" t="n">
-        <v>-0.06587899999999999</v>
+        <v>10.712403</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
@@ -36137,10 +36027,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Acquisition cost 4 -</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
+          <t>Depletion and depreciation 9 21,807,111</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -36177,7 +36071,7 @@
         </is>
       </c>
       <c r="L425" s="5" t="n">
-        <v>2.95636</v>
+        <v>7.75032</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
@@ -36208,10 +36102,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Gain on acquisition 4 -</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>Gross profit 18,115,158</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -36248,7 +36146,7 @@
         </is>
       </c>
       <c r="L426" s="5" t="n">
-        <v>-18.010552</v>
+        <v>7.249384</v>
       </c>
       <c r="M426" t="inlineStr">
         <is>
@@ -36279,10 +36177,14 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Contingent payment to Repsol 11 3,386,000</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>General and administrative 19 8,997,959</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -36318,10 +36220,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L427" s="5" t="n">
+        <v>4.215798</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
@@ -36352,7 +36252,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Write off Ecuadorian receivable 6 5,296,387</t>
+          <t>Financial cost (income) 21 95,995</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -36391,10 +36291,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L428" s="5" t="n">
+        <v>-0.167621</v>
       </c>
       <c r="M428" t="inlineStr">
         <is>
@@ -36425,7 +36323,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Write off capitalized exploration expenditure 10 2,240,368</t>
+          <t>Stock-based compensation 12 2,802,659</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -36464,10 +36362,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L429" s="5" t="n">
+        <v>0.767899</v>
       </c>
       <c r="M429" t="inlineStr">
         <is>
@@ -36498,7 +36394,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Other income 20 (1,136.533)</t>
+          <t>Foreign exchange gain (365,910)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -36538,7 +36434,7 @@
         </is>
       </c>
       <c r="L430" s="5" t="n">
-        <v>-0.268942</v>
+        <v>-0.06587899999999999</v>
       </c>
       <c r="M430" t="inlineStr">
         <is>
@@ -36569,7 +36465,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Net (loss) income before income taxes (3,201,767)</t>
+          <t>Acquisition cost 4 -</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -36609,7 +36505,7 @@
         </is>
       </c>
       <c r="L431" s="5" t="n">
-        <v>17.822321</v>
+        <v>2.95636</v>
       </c>
       <c r="M431" t="inlineStr">
         <is>
@@ -36640,7 +36536,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>5,561,401 (2,983,560) Current income tax recovery (expense)</t>
+          <t>Gain on acquisition 4 -</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -36680,7 +36576,7 @@
         </is>
       </c>
       <c r="L432" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>-18.010552</v>
       </c>
       <c r="M432" t="inlineStr">
         <is>
@@ -36711,14 +36607,10 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Total income tax expense 5,561,401</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Contingent payment to Repsol 11 3,386,000</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -36754,8 +36646,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L433" s="5" t="n">
-        <v>-2.98356</v>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M433" t="inlineStr">
         <is>
@@ -36786,14 +36680,10 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Net income $ 2,359,634 $</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write off Ecuadorian receivable 6 5,296,387</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -36829,8 +36719,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L434" s="5" t="n">
-        <v>14.838761</v>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
@@ -36856,12 +36748,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Translation reserve 1,687,005</t>
+          <t>Write off capitalized exploration expenditure 10 2,240,368</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -36900,8 +36792,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L435" s="5" t="n">
-        <v>0.370143</v>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M435" t="inlineStr">
         <is>
@@ -36927,19 +36821,15 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income $ 4,046,639 $</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other income 20 (1,136.533)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -36976,7 +36866,7 @@
         </is>
       </c>
       <c r="L436" s="5" t="n">
-        <v>15.208904</v>
+        <v>-0.268942</v>
       </c>
       <c r="M436" t="inlineStr">
         <is>
@@ -37002,12 +36892,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Basic $0.02</t>
+          <t>Net (loss) income before income taxes (3,201,767)</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -37047,7 +36937,7 @@
         </is>
       </c>
       <c r="L437" s="5" t="n">
-        <v>1.7e-07</v>
+        <v>17.822321</v>
       </c>
       <c r="M437" t="inlineStr">
         <is>
@@ -37073,15 +36963,19 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>22 Diluted $0.02</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr"/>
+          <t>5,561,401 (2,983,560) Current income tax recovery (expense)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -37118,7 +37012,7 @@
         </is>
       </c>
       <c r="L438" s="5" t="n">
-        <v>1.4e-07</v>
+        <v>2.6e-05</v>
       </c>
       <c r="M438" t="inlineStr">
         <is>
@@ -37144,15 +37038,19 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Services Revenue 17 $</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr"/>
+          <t>Total income tax expense 5,561,401</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -37189,7 +37087,7 @@
         </is>
       </c>
       <c r="L439" s="5" t="n">
-        <v>24.83227</v>
+        <v>-2.98356</v>
       </c>
       <c r="M439" t="inlineStr">
         <is>
@@ -37215,15 +37113,19 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Operator fees 17</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr"/>
+          <t>Net income $ 2,359,634 $</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -37260,7 +37162,7 @@
         </is>
       </c>
       <c r="L440" s="5" t="n">
-        <v>0.150089</v>
+        <v>14.838761</v>
       </c>
       <c r="M440" t="inlineStr">
         <is>
@@ -37286,12 +37188,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Other 17</t>
+          <t>Translation reserve 1,687,005</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -37331,7 +37233,7 @@
         </is>
       </c>
       <c r="L441" s="5" t="n">
-        <v>0.729748</v>
+        <v>0.370143</v>
       </c>
       <c r="M441" t="inlineStr">
         <is>
@@ -37357,17 +37259,17 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Operating expenses 18</t>
+          <t>Net income and comprehensive income $ 4,046,639 $</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -37406,7 +37308,7 @@
         </is>
       </c>
       <c r="L442" s="5" t="n">
-        <v>10.712403</v>
+        <v>15.208904</v>
       </c>
       <c r="M442" t="inlineStr">
         <is>
@@ -37432,19 +37334,15 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Net income per share</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Depletion and depreciation 9</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Basic $0.02</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -37481,7 +37379,7 @@
         </is>
       </c>
       <c r="L443" s="5" t="n">
-        <v>7.75032</v>
+        <v>1.7e-07</v>
       </c>
       <c r="M443" t="inlineStr">
         <is>
@@ -37507,19 +37405,15 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Net income per share</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>22 Diluted $0.02</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -37556,7 +37450,7 @@
         </is>
       </c>
       <c r="L444" s="5" t="n">
-        <v>7.249384</v>
+        <v>1.4e-07</v>
       </c>
       <c r="M444" t="inlineStr">
         <is>
@@ -37582,19 +37476,15 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>General and administrative 19</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Services Revenue 17 $</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -37625,11 +37515,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K445" s="5" t="n">
-        <v>1.140409</v>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L445" s="5" t="n">
-        <v>4.215798</v>
+        <v>24.83227</v>
       </c>
       <c r="M445" t="inlineStr">
         <is>
@@ -37655,12 +37547,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Financial (income) cost, net 21</t>
+          <t>Operator fees 17</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -37694,11 +37586,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K446" s="5" t="n">
-        <v>0.022438</v>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L446" s="5" t="n">
-        <v>-0.167621</v>
+        <v>0.150089</v>
       </c>
       <c r="M446" t="inlineStr">
         <is>
@@ -37724,12 +37618,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Operating cost and expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Stock-based compensation 12</t>
+          <t>Other 17</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
@@ -37763,11 +37657,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K447" s="5" t="n">
-        <v>0.022832</v>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L447" s="5" t="n">
-        <v>0.767899</v>
+        <v>0.729748</v>
       </c>
       <c r="M447" t="inlineStr">
         <is>
@@ -37798,12 +37694,12 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Operating expenses 18</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -37836,11 +37732,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K448" s="5" t="n">
-        <v>-0.094691</v>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L448" s="5" t="n">
-        <v>-0.06587899999999999</v>
+        <v>10.712403</v>
       </c>
       <c r="M448" t="inlineStr">
         <is>
@@ -37871,10 +37769,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Acquisition cost 4</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr"/>
+          <t>Depletion and depreciation 9</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -37911,7 +37813,7 @@
         </is>
       </c>
       <c r="L449" s="5" t="n">
-        <v>2.95636</v>
+        <v>7.75032</v>
       </c>
       <c r="M449" t="inlineStr">
         <is>
@@ -37942,10 +37844,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Gain on acquisition 4</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -37982,7 +37888,7 @@
         </is>
       </c>
       <c r="L450" s="5" t="n">
-        <v>-18.010552</v>
+        <v>7.249384</v>
       </c>
       <c r="M450" t="inlineStr">
         <is>
@@ -38013,10 +37919,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Other income, net 20</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr"/>
+          <t>General and administrative 19</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -38047,13 +37957,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K451" s="5" t="n">
+        <v>1.140409</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>-0.268942</v>
+        <v>4.215798</v>
       </c>
       <c r="M451" t="inlineStr">
         <is>
@@ -38084,14 +37992,10 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Net income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Financial (income) cost, net 21</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -38123,10 +38027,10 @@
         </is>
       </c>
       <c r="K452" s="5" t="n">
-        <v>-1.090988</v>
+        <v>0.022438</v>
       </c>
       <c r="L452" s="5" t="n">
-        <v>17.822321</v>
+        <v>-0.167621</v>
       </c>
       <c r="M452" t="inlineStr">
         <is>
@@ -38157,7 +38061,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Current income tax 26</t>
+          <t>Stock-based compensation 12</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -38191,13 +38095,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K453" s="5" t="n">
+        <v>0.022832</v>
       </c>
       <c r="L453" s="5" t="n">
-        <v>-2.98356</v>
+        <v>0.767899</v>
       </c>
       <c r="M453" t="inlineStr">
         <is>
@@ -38228,10 +38130,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Deferred income tax 26</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -38262,15 +38168,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K454" s="5" t="n">
+        <v>-0.094691</v>
+      </c>
+      <c r="L454" s="5" t="n">
+        <v>-0.06587899999999999</v>
       </c>
       <c r="M454" t="inlineStr">
         <is>
@@ -38301,14 +38203,10 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Total income tax expense</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Acquisition cost 4</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
@@ -38345,7 +38243,7 @@
         </is>
       </c>
       <c r="L455" s="5" t="n">
-        <v>-2.98356</v>
+        <v>2.95636</v>
       </c>
       <c r="M455" t="inlineStr">
         <is>
@@ -38376,14 +38274,10 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Net income (loss) $</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on acquisition 4</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -38414,11 +38308,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K456" s="5" t="n">
-        <v>-1.090988</v>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L456" s="5" t="n">
-        <v>14.838761</v>
+        <v>-18.010552</v>
       </c>
       <c r="M456" t="inlineStr">
         <is>
@@ -38444,12 +38340,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Translation reserve</t>
+          <t>Other income, net 20</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
@@ -38483,11 +38379,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K457" s="5" t="n">
-        <v>-0.007173</v>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L457" s="5" t="n">
-        <v>0.370143</v>
+        <v>-0.268942</v>
       </c>
       <c r="M457" t="inlineStr">
         <is>
@@ -38513,17 +38411,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) $</t>
+          <t>Net income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -38557,10 +38455,10 @@
         </is>
       </c>
       <c r="K458" s="5" t="n">
-        <v>-1.098161</v>
+        <v>-1.090988</v>
       </c>
       <c r="L458" s="5" t="n">
-        <v>15.208904</v>
+        <v>17.822321</v>
       </c>
       <c r="M458" t="inlineStr">
         <is>
@@ -38586,12 +38484,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Basic 22</t>
+          <t>Current income tax 26</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -38625,11 +38523,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K459" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L459" s="5" t="n">
-        <v>1.7e-07</v>
+        <v>-2.98356</v>
       </c>
       <c r="M459" t="inlineStr">
         <is>
@@ -38655,19 +38555,15 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>General and administrative 10 $</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Deferred income tax 26</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -38693,11 +38589,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J460" s="5" t="n">
-        <v>1.20376</v>
-      </c>
-      <c r="K460" s="5" t="n">
-        <v>1.140409</v>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -38728,17 +38628,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Total income tax expense</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -38751,25 +38651,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G461" s="5" t="n">
-        <v>0.115566</v>
-      </c>
-      <c r="H461" s="5" t="n">
-        <v>0.003731</v>
-      </c>
-      <c r="I461" s="5" t="n">
-        <v>0.003449</v>
-      </c>
-      <c r="J461" s="5" t="n">
-        <v>0.18968</v>
-      </c>
-      <c r="K461" s="5" t="n">
-        <v>0.022438</v>
-      </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L461" s="5" t="n">
+        <v>-2.98356</v>
       </c>
       <c r="M461" t="inlineStr">
         <is>
@@ -38795,15 +38703,19 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating cost and expenses</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr"/>
+          <t>Net income (loss) $</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -38829,16 +38741,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J462" s="5" t="n">
-        <v>0.005033</v>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K462" s="5" t="n">
-        <v>0.022832</v>
-      </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.090988</v>
+      </c>
+      <c r="L462" s="5" t="n">
+        <v>14.838761</v>
       </c>
       <c r="M462" t="inlineStr">
         <is>
@@ -38864,19 +38776,15 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Translation reserve</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -38902,16 +38810,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J463" s="5" t="n">
-        <v>0.067165</v>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K463" s="5" t="n">
-        <v>-0.094691</v>
-      </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007173</v>
+      </c>
+      <c r="L463" s="5" t="n">
+        <v>0.370143</v>
       </c>
       <c r="M463" t="inlineStr">
         <is>
@@ -38937,15 +38845,19 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt 9</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr"/>
+          <t>Net income (loss) and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -38971,18 +38883,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J464" s="5" t="n">
-        <v>-0.059083</v>
-      </c>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K464" s="5" t="n">
+        <v>-1.098161</v>
+      </c>
+      <c r="L464" s="5" t="n">
+        <v>15.208904</v>
       </c>
       <c r="M464" t="inlineStr">
         <is>
@@ -39008,19 +38918,15 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income (loss) per share</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Total expenses $</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Basic 22</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -39041,19 +38947,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I465" s="5" t="n">
-        <v>1.848084</v>
-      </c>
-      <c r="J465" s="5" t="n">
-        <v>1.406555</v>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K465" s="5" t="n">
-        <v>1.090988</v>
-      </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="L465" s="5" t="n">
+        <v>1.7e-07</v>
       </c>
       <c r="M465" t="inlineStr">
         <is>
@@ -39084,12 +38992,12 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>General and administrative 10 $</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -39112,14 +39020,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I466" s="5" t="n">
-        <v>-1.848084</v>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J466" s="5" t="n">
-        <v>-1.406555</v>
+        <v>1.20376</v>
       </c>
       <c r="K466" s="5" t="n">
-        <v>-1.090988</v>
+        <v>1.140409</v>
       </c>
       <c r="L466" t="inlineStr">
         <is>
@@ -39150,15 +39060,19 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Translation reserve</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -39169,24 +39083,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G467" s="5" t="n">
+        <v>0.115566</v>
+      </c>
+      <c r="H467" s="5" t="n">
+        <v>0.003731</v>
       </c>
       <c r="I467" s="5" t="n">
-        <v>-0.005361</v>
+        <v>0.003449</v>
       </c>
       <c r="J467" s="5" t="n">
-        <v>-0.005566</v>
+        <v>0.18968</v>
       </c>
       <c r="K467" s="5" t="n">
-        <v>0.007173</v>
+        <v>0.022438</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
@@ -39217,12 +39127,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
+          <t>Stock-based compensation 9</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
@@ -39246,14 +39156,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I468" s="5" t="n">
-        <v>1.842723</v>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J468" s="5" t="n">
-        <v>1.400989</v>
+        <v>0.005033</v>
       </c>
       <c r="K468" s="5" t="n">
-        <v>1.098161</v>
+        <v>0.022832</v>
       </c>
       <c r="L468" t="inlineStr">
         <is>
@@ -39284,17 +39196,17 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Basic and diluted 11</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -39323,10 +39235,10 @@
         </is>
       </c>
       <c r="J469" s="5" t="n">
-        <v>4e-08</v>
+        <v>0.067165</v>
       </c>
       <c r="K469" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.094691</v>
       </c>
       <c r="L469" t="inlineStr">
         <is>
@@ -39362,14 +39274,10 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>General and administrative 11 $</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Gain on settlement of debt 9</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -39390,11 +39298,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I470" s="5" t="n">
-        <v>2.292206</v>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J470" s="5" t="n">
-        <v>1.20376</v>
+        <v>-0.059083</v>
       </c>
       <c r="K470" t="inlineStr">
         <is>
@@ -39435,10 +39345,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Stock-based compensation 10</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr"/>
+          <t>Total expenses $</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -39454,19 +39368,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H471" s="5" t="n">
-        <v>0.854388</v>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I471" s="5" t="n">
-        <v>0.03708</v>
+        <v>1.848084</v>
       </c>
       <c r="J471" s="5" t="n">
-        <v>0.005033</v>
-      </c>
-      <c r="K471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.406555</v>
+      </c>
+      <c r="K471" s="5" t="n">
+        <v>1.090988</v>
       </c>
       <c r="L471" t="inlineStr">
         <is>
@@ -39502,12 +39416,12 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -39525,19 +39439,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H472" s="5" t="n">
-        <v>0.093306</v>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I472" s="5" t="n">
-        <v>0.016509</v>
+        <v>-1.848084</v>
       </c>
       <c r="J472" s="5" t="n">
-        <v>0.067165</v>
-      </c>
-      <c r="K472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.406555</v>
+      </c>
+      <c r="K472" s="5" t="n">
+        <v>-1.090988</v>
       </c>
       <c r="L472" t="inlineStr">
         <is>
@@ -39568,12 +39482,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt 10</t>
+          <t>Translation reserve</t>
         </is>
       </c>
       <c r="D473" t="inlineStr"/>
@@ -39597,18 +39511,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I473" s="5" t="n">
+        <v>-0.005361</v>
       </c>
       <c r="J473" s="5" t="n">
-        <v>-0.059083</v>
-      </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005566</v>
+      </c>
+      <c r="K473" s="5" t="n">
+        <v>0.007173</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -39639,12 +39549,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Gain on disposition of assets 6</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
@@ -39669,17 +39579,13 @@
         </is>
       </c>
       <c r="I474" s="5" t="n">
-        <v>-0.50116</v>
-      </c>
-      <c r="J474" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K474" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.842723</v>
+      </c>
+      <c r="J474" s="5" t="n">
+        <v>1.400989</v>
+      </c>
+      <c r="K474" s="5" t="n">
+        <v>1.098161</v>
       </c>
       <c r="L474" t="inlineStr">
         <is>
@@ -39715,7 +39621,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Basic and diluted 12</t>
+          <t>Basic and diluted 11</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -39743,16 +39649,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I475" s="5" t="n">
-        <v>5e-08</v>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J475" s="5" t="n">
         <v>4e-08</v>
       </c>
-      <c r="K475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K475" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="L475" t="inlineStr">
         <is>
@@ -39783,17 +39689,17 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>General and administrative 11 $</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -39816,15 +39722,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I476" s="5" t="n">
+        <v>2.292206</v>
+      </c>
+      <c r="J476" s="5" t="n">
+        <v>1.20376</v>
       </c>
       <c r="K476" t="inlineStr">
         <is>
@@ -39860,19 +39762,15 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Revenues total</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Stock-based compensation 10</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -39888,20 +39786,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H477" s="5" t="n">
+        <v>0.854388</v>
+      </c>
+      <c r="I477" s="5" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="J477" s="5" t="n">
+        <v>0.005033</v>
       </c>
       <c r="K477" t="inlineStr">
         <is>
@@ -39942,12 +39834,12 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -39960,19 +39852,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G478" s="5" t="n">
-        <v>0.031591</v>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H478" s="5" t="n">
-        <v>1.844188</v>
+        <v>0.093306</v>
       </c>
       <c r="I478" s="5" t="n">
-        <v>2.292206</v>
-      </c>
-      <c r="J478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016509</v>
+      </c>
+      <c r="J478" s="5" t="n">
+        <v>0.067165</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
@@ -40013,7 +39905,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Loss (Gain) on sale of assets 6</t>
+          <t>Gain on settlement of debt 10</t>
         </is>
       </c>
       <c r="D479" t="inlineStr"/>
@@ -40032,16 +39924,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H479" s="5" t="n">
-        <v>0.083686</v>
-      </c>
-      <c r="I479" s="5" t="n">
-        <v>-0.50116</v>
-      </c>
-      <c r="J479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J479" s="5" t="n">
+        <v>-0.059083</v>
       </c>
       <c r="K479" t="inlineStr">
         <is>
@@ -40082,30 +39976,32 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Gain on disposition of assets 6</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F480" s="5" t="n">
-        <v>0.315003</v>
-      </c>
-      <c r="G480" s="5" t="n">
-        <v>0.156934</v>
-      </c>
-      <c r="H480" s="5" t="n">
-        <v>2.879299</v>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I480" s="5" t="n">
-        <v>1.848084</v>
+        <v>-0.50116</v>
       </c>
       <c r="J480" t="inlineStr">
         <is>
@@ -40146,17 +40042,17 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Basic and diluted 12</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -40169,19 +40065,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G481" s="5" t="n">
-        <v>-0.156934</v>
-      </c>
-      <c r="H481" s="5" t="n">
-        <v>-2.879299</v>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I481" s="5" t="n">
-        <v>-1.848084</v>
-      </c>
-      <c r="J481" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-08</v>
+      </c>
+      <c r="J481" s="5" t="n">
+        <v>4e-08</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
@@ -40217,15 +40115,19 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Translation reserve</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr"/>
+          <t>Revenues</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -40241,11 +40143,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H482" s="5" t="n">
-        <v>-0.000725</v>
-      </c>
-      <c r="I482" s="5" t="n">
-        <v>0.005361</v>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
@@ -40286,15 +40192,19 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr"/>
+          <t>Revenues total</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -40305,14 +40215,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G483" s="5" t="n">
-        <v>-0.156934</v>
-      </c>
-      <c r="H483" s="5" t="n">
-        <v>-2.880024</v>
-      </c>
-      <c r="I483" s="5" t="n">
-        <v>-1.842723</v>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
@@ -40358,10 +40274,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Stock-based compensation 11</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -40372,18 +40292,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G484" s="5" t="n">
+        <v>0.031591</v>
       </c>
       <c r="H484" s="5" t="n">
-        <v>0.854388</v>
-      </c>
-      <c r="I484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.844188</v>
+      </c>
+      <c r="I484" s="5" t="n">
+        <v>2.292206</v>
       </c>
       <c r="J484" t="inlineStr">
         <is>
@@ -40429,7 +40345,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Loss on sale of assets 14</t>
+          <t>Loss (Gain) on sale of assets 6</t>
         </is>
       </c>
       <c r="D485" t="inlineStr"/>
@@ -40451,10 +40367,8 @@
       <c r="H485" s="5" t="n">
         <v>0.083686</v>
       </c>
-      <c r="I485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I485" s="5" t="n">
+        <v>-0.50116</v>
       </c>
       <c r="J485" t="inlineStr">
         <is>
@@ -40500,30 +40414,28 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr"/>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E486" s="5" t="n">
+        <v>0.321823</v>
       </c>
       <c r="F486" s="5" t="n">
-        <v>0.006423</v>
+        <v>0.315003</v>
       </c>
       <c r="G486" s="5" t="n">
-        <v>0.009776999999999999</v>
-      </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.156934</v>
+      </c>
+      <c r="H486" s="5" t="n">
+        <v>2.879299</v>
+      </c>
+      <c r="I486" s="5" t="n">
+        <v>1.848084</v>
       </c>
       <c r="J486" t="inlineStr">
         <is>
@@ -40562,33 +40474,39 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr"/>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>March 31, 2017 March</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F487" s="5" t="n">
-        <v>0.002016</v>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G487" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.156934</v>
+      </c>
+      <c r="H487" s="5" t="n">
+        <v>-2.879299</v>
+      </c>
+      <c r="I487" s="5" t="n">
+        <v>-1.848084</v>
       </c>
       <c r="J487" t="inlineStr">
         <is>
@@ -40627,17 +40545,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr"/>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Loss</t>
+        </is>
+      </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Interest and other income $</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Translation reserve</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -40653,15 +40571,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H488" s="5" t="n">
+        <v>-0.000725</v>
+      </c>
+      <c r="I488" s="5" t="n">
+        <v>0.005361</v>
       </c>
       <c r="J488" t="inlineStr">
         <is>
@@ -40702,39 +40616,33 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Comprehensive Loss</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F489" s="5" t="n">
-        <v>0.182787</v>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G489" s="5" t="n">
-        <v>0.031591</v>
-      </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.156934</v>
+      </c>
+      <c r="H489" s="5" t="n">
+        <v>-2.880024</v>
+      </c>
+      <c r="I489" s="5" t="n">
+        <v>-1.842723</v>
       </c>
       <c r="J489" t="inlineStr">
         <is>
@@ -40780,29 +40688,27 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Interest expense (Note 9, 13)</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Stock-based compensation 11</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F490" s="5" t="n">
-        <v>0.125793</v>
-      </c>
-      <c r="G490" s="5" t="n">
-        <v>0.115566</v>
-      </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H490" s="5" t="n">
+        <v>0.854388</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
@@ -40853,29 +40759,27 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on sale of assets 14</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F491" s="5" t="n">
-        <v>-0.315003</v>
-      </c>
-      <c r="G491" s="5" t="n">
-        <v>-0.156934</v>
-      </c>
-      <c r="H491" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H491" s="5" t="n">
+        <v>0.083686</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
@@ -40926,20 +40830,18 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Deficit - start of year</t>
+          <t>Exploration and evaluation expenses</t>
         </is>
       </c>
       <c r="D492" t="inlineStr"/>
-      <c r="E492" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E492" s="5" t="n">
+        <v>0.02657</v>
       </c>
       <c r="F492" s="5" t="n">
-        <v>-12.067781</v>
+        <v>0.006423</v>
       </c>
       <c r="G492" s="5" t="n">
-        <v>-12.225722</v>
+        <v>0.009776999999999999</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
@@ -40988,14 +40890,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B493" t="inlineStr"/>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Options expired during year</t>
+          <t>March 31, 2017 March</t>
         </is>
       </c>
       <c r="D493" t="inlineStr"/>
@@ -41005,10 +40903,10 @@
         </is>
       </c>
       <c r="F493" s="5" t="n">
-        <v>0.157062</v>
+        <v>0.002016</v>
       </c>
       <c r="G493" s="5" t="n">
-        <v>0.009712999999999999</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H493" t="inlineStr">
         <is>
@@ -41057,68 +40955,559 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Interest and other income $</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E494" s="5" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>General and administration</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E495" s="5" t="n">
+        <v>0.173842</v>
+      </c>
+      <c r="F495" s="5" t="n">
+        <v>0.182787</v>
+      </c>
+      <c r="G495" s="5" t="n">
+        <v>0.031591</v>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Interest expense (Note 9, 13)</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E496" s="5" t="n">
+        <v>0.121411</v>
+      </c>
+      <c r="F496" s="5" t="n">
+        <v>0.125793</v>
+      </c>
+      <c r="G496" s="5" t="n">
+        <v>0.115566</v>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E497" s="5" t="n">
+        <v>-0.32181</v>
+      </c>
+      <c r="F497" s="5" t="n">
+        <v>-0.315003</v>
+      </c>
+      <c r="G497" s="5" t="n">
+        <v>-0.156934</v>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Deficit - start of year</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" s="5" t="n">
+        <v>-11.793663</v>
+      </c>
+      <c r="F498" s="5" t="n">
+        <v>-12.067781</v>
+      </c>
+      <c r="G498" s="5" t="n">
+        <v>-12.225722</v>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Options expired during year</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
+      <c r="E499" s="5" t="n">
+        <v>0.047692</v>
+      </c>
+      <c r="F499" s="5" t="n">
+        <v>0.157062</v>
+      </c>
+      <c r="G499" s="5" t="n">
+        <v>0.009712999999999999</v>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
         <is>
           <t>Deficit - end of year                                              $(12,372,943)           $(12,225,722)</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
+      <c r="C500" t="inlineStr">
         <is>
           <t>Weighted average shares outstanding</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr">
+      <c r="D500" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F494" s="5" t="n">
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F500" s="5" t="n">
         <v>51.137679</v>
       </c>
-      <c r="G494" s="5" t="n">
+      <c r="G500" s="5" t="n">
         <v>51.137679</v>
       </c>
-      <c r="H494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O494" t="inlineStr">
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E501" s="5" t="n">
+        <v>51.137679</v>
+      </c>
+      <c r="F501" s="5" t="n">
+        <v>51.137679</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
         <is>
           <t>-</t>
         </is>
